--- a/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le feu vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue. Maman dit : le feu vert, c'est le signal. On avance ensemble. Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
+          <t>Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le feu vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue. Le feu vert, c'est le signal. On avance ensemble. Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le feu vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue.
+maman|Le feu vert, c'est le signal. On avance ensemble.
+narrateur|Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est au passage. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a attendu le feu vert. La main était tenue. L'adulte guidait. Lila a entendu la règle aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo porte le sac d'oranges. Maman ouvre la porte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Kenzo est au passage. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1685,7 @@
           <t>narrateur|Kenzo a attendu le feu vert. La main était tenue. L'adulte guidait. Lila a entendu la règle aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1853,7 @@
           <t>narrateur|Kenzo porte le sac d'oranges. Maman ouvre la porte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo et le feu vert</t>
+          <t>L'auvent mouillé</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous l'auvent mouillé, Sarah et Chouchou rentrent du marché. Deux rues. Un citron roule. Elles serrent la main, attendent le vert deux fois.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le feu vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue. Le feu vert, c'est le signal. On avance ensemble. Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
+          <t>L'auvent du marché goutte encore. Une goutte tombe sur une caisse d'oranges. La toile mouillée sent l'eau et le citron. Sarah tient un sac de toile, déjà un peu lourd. Chouchou marche à côté, capuche encore humide. Maman porte le second sac, plus rond. Tu as vu la goutte sur l'orange, Sarah ? Elle brille. Moi, je veux un citron. On en prend un, alors. En ce moment, Sarah pose le citron dans le sac. Il est froid, un peu rêche. On rentre ? Oui. On marche sur le trottoir. Elles quittent l'auvent. Le pavé est sombre et luisant. Une orange roule dans le sac, tout doux. Ça sent bon. Le premier passage arrive, tout large. On s'arrête. Tu donnes la main ? Sarah donne la main. Chouchou prend l'autre main. Le petit bonhomme est encore rouge. On attend le vert. Un vélo glisse au loin, sans bruit. Il est long, le rouge. On attend ensemble. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles avancent avec maman, sans se lâcher. Le sac tape la jambe de Sarah. Une deuxième rue s'ouvre, plus étroite. Un bus souffle au loin. Le citron glisse du sac. Il roule vers la bordure. Le citron ! Je le prends ! On reste sur le trottoir. Sarah, tu serres ma main ? Sarah serre la main. Elle pose les pieds au bord, et elle attend. Chouchou s'arrête aussi, capuche trempée. Le citron s'immobilise contre une feuille mouillée. Le petit bonhomme est rouge, encore. On attend le vert. Merci, Sarah. J'attends. Moi aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue. Maman dit : le feu vert, c'est le signal. On avance ensemble. Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'auvent du marché goutte encore. Une goutte tombe sur une caisse d'oranges. La toile mouillée sent l'eau et le citron. Sarah tient un sac de toile, déjà un peu lourd. Chouchou marche à côté, capuche encore humide. Maman porte le second sac, plus rond. Tu as vu la goutte sur l'orange, Sarah ? Elle brille. Moi, je veux un citron. On en prend un, alors. En ce moment, Sarah pose le citron dans le sac. Il est froid, un peu rêche. On rentre ? Oui. On marche sur le trottoir. Elles quittent l'auvent. Le pavé est sombre et luisant. Une orange roule dans le sac, tout doux. Ça sent bon. Le premier passage arrive, tout large. On s'arrête. Tu donnes la main ? Sarah donne la main. Chouchou prend l'autre main. Le petit bonhomme est encore rouge. On attend le vert. Un vélo glisse au loin, sans bruit. Il est long, le rouge. On attend ensemble. Puis le petit bonhomme devient vert. Feu vert. On avance ensemble. Elles avancent avec maman, sans se lâcher. Le sac tape la jambe de Sarah. Une deuxième rue s'ouvre, plus étroite. Un bus souffle au loin. Le citron glisse du sac. Il roule vers la bordure. Le citron ! Je le prends ! On reste sur le trottoir. Sarah, tu serres ma main ? Sarah serre la main. Elle pose les pieds au bord, et elle attend. Chouchou s'arrête aussi, capuche trempée. Le citron s'immobilise contre une feuille mouillée. Le petit bonhomme est rouge, encore. On attend le vert. Merci, Sarah. J'attends. Moi aussi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,9 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo rentre du marché avec maman. Le sac sent les oranges. Sa petite sœur Lila marche avec eux. Ils arrivent au passage. Kenzo pose les pieds sur le trottoir. Il donne la main à maman. Lila donne la main aussi. Ils restent sur le trottoir en attendant. Kenzo comprend la règle. On attend le feu vert. Parce qu'on attend le feu vert, on avance ensuite avec l'adulte. La main reste tenue.
-maman|Le feu vert, c'est le signal. On avance ensemble.
-narrateur|Kenzo marche. Ses pieds suivent maman. L'adulte guide Lila et Kenzo. De l'autre côté, Kenzo dit à Lila : main, feu vert, avec l'adulte. Maman serre les deux mains. Kenzo est fier.</t>
+          <t>narrateur|L'auvent du marché goutte encore.
+narrateur|Une goutte tombe sur une caisse d'oranges.
+narrateur|La toile mouillée sent l'eau et le citron.
+narrateur|Sarah tient un sac de toile, déjà un peu lourd.
+narrateur|Chouchou marche à côté, capuche encore humide.
+narrateur|Maman porte le second sac, plus rond.
+maman|Tu as vu la goutte sur l'orange, Sarah ?
+enfant-f|Elle brille.
+copine|Moi, je veux un citron.
+maman|On en prend un, alors.
+narrateur|En ce moment, Sarah pose le citron dans le sac.
+narrateur|Il est froid, un peu rêche.
+enfant-f|On rentre ?
+maman|Oui.
+maman|On marche sur le trottoir.
+narrateur|Elles quittent l'auvent.
+narrateur|Le pavé est sombre et luisant.
+narrateur|Une orange roule dans le sac, tout doux.
+copine|Ça sent bon.
+narrateur|Le premier passage arrive, tout large.
+maman|On s'arrête.
+maman|Tu donnes la main ?
+narrateur|Sarah donne la main.
+narrateur|Chouchou prend l'autre main.
+narrateur|Le petit bonhomme est encore rouge.
+maman|On attend le vert.
+narrateur|Un vélo glisse au loin, sans bruit.
+enfant-f|Il est long, le rouge.
+maman|On attend ensemble.
+narrateur|Puis le petit bonhomme devient vert.
+maman|Feu vert.
+maman|On avance ensemble.
+narrateur|Elles avancent avec maman, sans se lâcher.
+narrateur|Le sac tape la jambe de Sarah.
+narrateur|Une deuxième rue s'ouvre, plus étroite.
+narrateur|Un bus souffle au loin.
+narrateur|Le citron glisse du sac.
+narrateur|Il roule vers la bordure.
+copine|Le citron !
+copine|Je le prends !
+maman|On reste sur le trottoir.
+maman|Sarah, tu serres ma main ?
+narrateur|Sarah serre la main.
+narrateur|Elle pose les pieds au bord, et elle attend.
+narrateur|Chouchou s'arrête aussi, capuche trempée.
+narrateur|Le citron s'immobilise contre une feuille mouillée.
+narrateur|Le petit bonhomme est rouge, encore.
+maman|On attend le vert.
+maman|Merci, Sarah.
+enfant-f|J'attends.
+copine|Moi aussi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,12 +1406,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est au passage. Que fait-il ?</t>
+          <t>Sarah est au passage, avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Kenzo est au passage. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est au passage, avec maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1366,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>feu vert | la main | avec maman | avec l'adulte | attendre</t>
+          <t>feu vert | la main | avec maman | avec papa | avec l'adulte | attendre | le vert</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1381,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il attend le feu vert. Il donne la main. Il avance avec l'adulte. Que fait Kenzo ?</t>
+          <t>Elle donne la main. Elle attend le feu vert. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1490,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo est au passage. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah est au passage, avec maman.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a attendu le feu vert. La main était tenue. L'adulte guidait. Lila a entendu la règle aussi.</t>
+          <t>Sarah a serré la main. Elle a attendu le feu vert. Chouchou a attendu aussi, sur le trottoir. Vous avez attendu le vert ? Oui, maman. Oui. Le citron brille encore contre la feuille. Les sacs sentent l'auvent mouillé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Kenzo a attendu le &lt;emphasis level="moderate"&gt;feu&lt;/emphasis&gt; vert. La main était tenue. L'adulte guidait. Lila a entendu la règle aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a serré la main. Elle a attendu le feu vert. Chouchou a attendu aussi, sur le trottoir. Vous avez attendu le vert ? Oui, maman. Oui. Le citron brille encore contre la feuille. Les sacs sentent l'auvent mouillé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1655,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1682,10 +1742,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a attendu le feu vert. La main était tenue. L'adulte guidait. Lila a entendu la règle aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a serré la main.
+narrateur|Elle a attendu le feu vert.
+narrateur|Chouchou a attendu aussi, sur le trottoir.
+maman|Vous avez attendu le vert ?
+enfant-f|Oui, maman.
+copine|Oui.
+narrateur|Le citron brille encore contre la feuille.
+narrateur|Les sacs sentent l'auvent mouillé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1710,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo porte le sac d'oranges. Maman ouvre la porte.</t>
+          <t>Le petit bonhomme devient vert. Feu vert. On avance ensemble. Sarah ramasse le citron, sur le trottoir. Il est froid et un peu luisant. Il est à nous. On le met dans le sac. Elles avancent avec maman jusqu'à la porte. La clé fait un petit clic. Vous posez les sacs ? Oui. Les oranges roulent dans le saladier. Ça sent le marché, encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Kenzo porte le sac d'oranges. Maman ouvre la porte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit bonhomme devient vert. Feu vert. On avance ensemble. Sarah ramasse le citron, sur le trottoir. Il est froid et un peu luisant. Il est à nous. On le met dans le sac. Elles avancent avec maman jusqu'à la porte. La clé fait un petit clic. Vous posez les sacs ? Oui. Les oranges roulent dans le saladier. Ça sent le marché, encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1837,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1850,10 +1916,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo porte le sac d'oranges. Maman ouvre la porte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le petit bonhomme devient vert.
+maman|Feu vert.
+maman|On avance ensemble.
+narrateur|Sarah ramasse le citron, sur le trottoir.
+narrateur|Il est froid et un peu luisant.
+copine|Il est à nous.
+enfant-f|On le met dans le sac.
+narrateur|Elles avancent avec maman jusqu'à la porte.
+narrateur|La clé fait un petit clic.
+maman|Vous posez les sacs ?
+enfant-f|Oui.
+narrateur|Les oranges roulent dans le saladier.
+narrateur|Ça sent le marché, encore.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah frotte une orange contre sa joue. La peau est froide, un peu cireuse. Ça sent l'auvent. Oui. La toile mouillée sent encore l'orange.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah frotte une orange contre sa joue. La peau est froide, un peu cireuse. Ça sent l'auvent. Oui. La toile mouillée sent encore l'orange.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,7 +2016,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2018,10 +2095,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah frotte une orange contre sa joue.
+narrateur|La peau est froide, un peu cireuse.
+copine|Ça sent l'auvent.
+maman|Oui.
+narrateur|La toile mouillée sent encore l'orange.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.002-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>retour du marché</t>
+          <t>marché sous un auvent mouillé, deux rues vers la maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, Lila, maman</t>
+          <t>Sarah, Chouchou, maman</t>
         </is>
       </c>
     </row>
